--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,22 +12497,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15395,10 +15395,10 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15536,10 +15536,10 @@
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB107" t="n">
         <v>0</v>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO139"/>
+  <dimension ref="A1:AO140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11969,13 +11969,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -12005,16 +12005,16 @@
         <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12483,7 +12483,7 @@
         <v>0</v>
       </c>
       <c r="AO85" s="3" t="n">
-        <v>45891.65625</v>
+        <v>45891.64583333334</v>
       </c>
     </row>
     <row r="86">
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14889,27 +14889,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15021,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="AO103" s="3" t="n">
-        <v>45891.66666666666</v>
+        <v>45891.65625</v>
       </c>
     </row>
     <row r="104">
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15594,12 +15594,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15726,7 +15726,7 @@
         <v>0</v>
       </c>
       <c r="AO108" s="3" t="n">
-        <v>45891.67708333334</v>
+        <v>45891.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16431,7 +16431,7 @@
         <v>0</v>
       </c>
       <c r="AO113" s="3" t="n">
-        <v>45891.6875</v>
+        <v>45891.67708333334</v>
       </c>
     </row>
     <row r="114">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16722,27 +16722,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16854,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="AO116" s="3" t="n">
-        <v>45891.79166666666</v>
+        <v>45891.6875</v>
       </c>
     </row>
     <row r="117">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18555,12 +18555,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18687,7 +18687,7 @@
         <v>0</v>
       </c>
       <c r="AO129" s="3" t="n">
-        <v>45891.83333333334</v>
+        <v>45891.79166666666</v>
       </c>
     </row>
     <row r="130">
@@ -18837,12 +18837,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18969,7 +18969,7 @@
         <v>0</v>
       </c>
       <c r="AO131" s="3" t="n">
-        <v>45891.85416666666</v>
+        <v>45891.83333333334</v>
       </c>
     </row>
     <row r="132">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19110,7 +19110,7 @@
         <v>0</v>
       </c>
       <c r="AO132" s="3" t="n">
-        <v>45891.875</v>
+        <v>45891.85416666666</v>
       </c>
     </row>
     <row r="133">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19542,12 +19542,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19674,7 +19674,7 @@
         <v>0</v>
       </c>
       <c r="AO136" s="3" t="n">
-        <v>45891.89583333334</v>
+        <v>45891.875</v>
       </c>
     </row>
     <row r="137">
@@ -19824,12 +19824,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19956,7 +19956,7 @@
         <v>0</v>
       </c>
       <c r="AO138" s="3" t="n">
-        <v>45891.89930555555</v>
+        <v>45891.89583333334</v>
       </c>
     </row>
     <row r="139">
@@ -19965,138 +19965,279 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO139" s="3" t="n">
+        <v>45891.89930555555</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Forge FC</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO139" s="3" t="n">
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO140" s="3" t="n">
         <v>45891.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO140"/>
+  <dimension ref="A1:AO142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45891.45833333334</v>
+        <v>45891.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2058,27 +2058,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>45891.5</v>
+        <v>45891.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5151,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45891.52083333334</v>
+        <v>45891.5</v>
       </c>
     </row>
     <row r="34">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5301,27 +5301,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45891.54166666666</v>
+        <v>45891.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
-        <v>45891.54166666666</v>
+        <v>45891.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45891.5625</v>
+        <v>45891.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="AO44" s="3" t="n">
-        <v>45891.5625</v>
+        <v>45891.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7134,27 +7134,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45891.58333333334</v>
+        <v>45891.5625</v>
       </c>
     </row>
     <row r="49">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45891.58333333334</v>
+        <v>45891.5625</v>
       </c>
     </row>
     <row r="50">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45891.60416666666</v>
+        <v>45891.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -7839,27 +7839,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="AO53" s="3" t="n">
-        <v>45891.60416666666</v>
+        <v>45891.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>45891.625</v>
+        <v>45891.60416666666</v>
       </c>
     </row>
     <row r="68">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>45891.625</v>
+        <v>45891.60416666666</v>
       </c>
     </row>
     <row r="69">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11355,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="AO77" s="3" t="n">
-        <v>45891.63541666666</v>
+        <v>45891.625</v>
       </c>
     </row>
     <row r="78">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11496,7 +11496,7 @@
         <v>0</v>
       </c>
       <c r="AO78" s="3" t="n">
-        <v>45891.63541666666</v>
+        <v>45891.625</v>
       </c>
     </row>
     <row r="79">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11637,7 +11637,7 @@
         <v>0</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>45891.64583333334</v>
+        <v>45891.63541666666</v>
       </c>
     </row>
     <row r="80">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11778,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>45891.64583333334</v>
+        <v>45891.63541666666</v>
       </c>
     </row>
     <row r="81">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11828,13 +11828,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12492,27 +12492,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12624,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="AO86" s="3" t="n">
-        <v>45891.65625</v>
+        <v>45891.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="AO87" s="3" t="n">
-        <v>45891.65625</v>
+        <v>45891.64583333334</v>
       </c>
     </row>
     <row r="88">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,22 +12920,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,10 +13133,10 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15030,12 +15030,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15162,7 +15162,7 @@
         <v>0</v>
       </c>
       <c r="AO104" s="3" t="n">
-        <v>45891.66666666666</v>
+        <v>45891.65625</v>
       </c>
     </row>
     <row r="105">
@@ -15171,27 +15171,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15303,7 +15303,7 @@
         <v>0</v>
       </c>
       <c r="AO105" s="3" t="n">
-        <v>45891.66666666666</v>
+        <v>45891.65625</v>
       </c>
     </row>
     <row r="106">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15536,10 +15536,10 @@
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
         <v>0</v>
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15735,27 +15735,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15867,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="AO109" s="3" t="n">
-        <v>45891.67708333334</v>
+        <v>45891.66666666666</v>
       </c>
     </row>
     <row r="110">
@@ -15876,12 +15876,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="AO110" s="3" t="n">
-        <v>45891.67708333334</v>
+        <v>45891.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16440,12 +16440,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16572,7 +16572,7 @@
         <v>0</v>
       </c>
       <c r="AO114" s="3" t="n">
-        <v>45891.6875</v>
+        <v>45891.67708333334</v>
       </c>
     </row>
     <row r="115">
@@ -16581,12 +16581,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16713,7 +16713,7 @@
         <v>0</v>
       </c>
       <c r="AO115" s="3" t="n">
-        <v>45891.6875</v>
+        <v>45891.67708333334</v>
       </c>
     </row>
     <row r="116">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16863,27 +16863,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16995,7 +16995,7 @@
         <v>0</v>
       </c>
       <c r="AO117" s="3" t="n">
-        <v>45891.79166666666</v>
+        <v>45891.6875</v>
       </c>
     </row>
     <row r="118">
@@ -17004,27 +17004,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17136,7 +17136,7 @@
         <v>0</v>
       </c>
       <c r="AO118" s="3" t="n">
-        <v>45891.79166666666</v>
+        <v>45891.6875</v>
       </c>
     </row>
     <row r="119">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18828,7 +18828,7 @@
         <v>0</v>
       </c>
       <c r="AO130" s="3" t="n">
-        <v>45891.83333333334</v>
+        <v>45891.79166666666</v>
       </c>
     </row>
     <row r="131">
@@ -18837,12 +18837,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18969,7 +18969,7 @@
         <v>0</v>
       </c>
       <c r="AO131" s="3" t="n">
-        <v>45891.83333333334</v>
+        <v>45891.79166666666</v>
       </c>
     </row>
     <row r="132">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19110,7 +19110,7 @@
         <v>0</v>
       </c>
       <c r="AO132" s="3" t="n">
-        <v>45891.85416666666</v>
+        <v>45891.83333333334</v>
       </c>
     </row>
     <row r="133">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19251,7 +19251,7 @@
         <v>0</v>
       </c>
       <c r="AO133" s="3" t="n">
-        <v>45891.875</v>
+        <v>45891.83333333334</v>
       </c>
     </row>
     <row r="134">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19392,7 +19392,7 @@
         <v>0</v>
       </c>
       <c r="AO134" s="3" t="n">
-        <v>45891.875</v>
+        <v>45891.85416666666</v>
       </c>
     </row>
     <row r="135">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19683,12 +19683,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19815,7 +19815,7 @@
         <v>0</v>
       </c>
       <c r="AO137" s="3" t="n">
-        <v>45891.89583333334</v>
+        <v>45891.875</v>
       </c>
     </row>
     <row r="138">
@@ -19824,12 +19824,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19956,7 +19956,7 @@
         <v>0</v>
       </c>
       <c r="AO138" s="3" t="n">
-        <v>45891.89583333334</v>
+        <v>45891.875</v>
       </c>
     </row>
     <row r="139">
@@ -19965,12 +19965,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20097,7 +20097,7 @@
         <v>0</v>
       </c>
       <c r="AO139" s="3" t="n">
-        <v>45891.89930555555</v>
+        <v>45891.89583333334</v>
       </c>
     </row>
     <row r="140">
@@ -20106,138 +20106,420 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO140" s="3" t="n">
+        <v>45891.89583333334</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="3" t="n">
+        <v>45891.89930555555</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Forge FC</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO140" s="3" t="n">
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="3" t="n">
         <v>45891.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO142"/>
+  <dimension ref="A1:AO144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="AO45" s="3" t="n">
-        <v>45891.5625</v>
+        <v>45891.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45891.58333333334</v>
+        <v>45891.5625</v>
       </c>
     </row>
     <row r="51">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7980,27 +7980,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45891.60416666666</v>
+        <v>45891.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>45891.625</v>
+        <v>45891.60416666666</v>
       </c>
     </row>
     <row r="70">
@@ -10236,27 +10236,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>45891.625</v>
+        <v>45891.62152777778</v>
       </c>
     </row>
     <row r="71">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11637,7 +11637,7 @@
         <v>0</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>45891.63541666666</v>
+        <v>45891.625</v>
       </c>
     </row>
     <row r="80">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11778,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>45891.63541666666</v>
+        <v>45891.625</v>
       </c>
     </row>
     <row r="81">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11828,13 +11828,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11919,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>45891.64583333334</v>
+        <v>45891.63541666666</v>
       </c>
     </row>
     <row r="82">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12060,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="AO82" s="3" t="n">
-        <v>45891.64583333334</v>
+        <v>45891.63541666666</v>
       </c>
     </row>
     <row r="83">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12774,27 +12774,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,10 +12851,10 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
@@ -12906,7 +12906,7 @@
         <v>0</v>
       </c>
       <c r="AO88" s="3" t="n">
-        <v>45891.65625</v>
+        <v>45891.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13047,7 +13047,7 @@
         <v>0</v>
       </c>
       <c r="AO89" s="3" t="n">
-        <v>45891.65625</v>
+        <v>45891.64583333334</v>
       </c>
     </row>
     <row r="90">
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,10 +13133,10 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15312,12 +15312,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15444,7 +15444,7 @@
         <v>0</v>
       </c>
       <c r="AO106" s="3" t="n">
-        <v>45891.66666666666</v>
+        <v>45891.65625</v>
       </c>
     </row>
     <row r="107">
@@ -15453,27 +15453,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15585,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="AO107" s="3" t="n">
-        <v>45891.66666666666</v>
+        <v>45891.65625</v>
       </c>
     </row>
     <row r="108">
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -16017,12 +16017,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16149,7 +16149,7 @@
         <v>0</v>
       </c>
       <c r="AO111" s="3" t="n">
-        <v>45891.67708333334</v>
+        <v>45891.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -16158,27 +16158,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16290,7 +16290,7 @@
         <v>0</v>
       </c>
       <c r="AO112" s="3" t="n">
-        <v>45891.67708333334</v>
+        <v>45891.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16722,12 +16722,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16854,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="AO116" s="3" t="n">
-        <v>45891.6875</v>
+        <v>45891.67708333334</v>
       </c>
     </row>
     <row r="117">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16995,7 +16995,7 @@
         <v>0</v>
       </c>
       <c r="AO117" s="3" t="n">
-        <v>45891.6875</v>
+        <v>45891.67708333334</v>
       </c>
     </row>
     <row r="118">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17145,27 +17145,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17277,7 +17277,7 @@
         <v>0</v>
       </c>
       <c r="AO119" s="3" t="n">
-        <v>45891.79166666666</v>
+        <v>45891.6875</v>
       </c>
     </row>
     <row r="120">
@@ -17286,27 +17286,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17418,7 +17418,7 @@
         <v>0</v>
       </c>
       <c r="AO120" s="3" t="n">
-        <v>45891.79166666666</v>
+        <v>45891.6875</v>
       </c>
     </row>
     <row r="121">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19110,7 +19110,7 @@
         <v>0</v>
       </c>
       <c r="AO132" s="3" t="n">
-        <v>45891.83333333334</v>
+        <v>45891.79166666666</v>
       </c>
     </row>
     <row r="133">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19251,7 +19251,7 @@
         <v>0</v>
       </c>
       <c r="AO133" s="3" t="n">
-        <v>45891.83333333334</v>
+        <v>45891.79166666666</v>
       </c>
     </row>
     <row r="134">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19392,7 +19392,7 @@
         <v>0</v>
       </c>
       <c r="AO134" s="3" t="n">
-        <v>45891.85416666666</v>
+        <v>45891.83333333334</v>
       </c>
     </row>
     <row r="135">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19533,7 +19533,7 @@
         <v>0</v>
       </c>
       <c r="AO135" s="3" t="n">
-        <v>45891.875</v>
+        <v>45891.83333333334</v>
       </c>
     </row>
     <row r="136">
@@ -19542,12 +19542,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19674,7 +19674,7 @@
         <v>0</v>
       </c>
       <c r="AO136" s="3" t="n">
-        <v>45891.875</v>
+        <v>45891.85416666666</v>
       </c>
     </row>
     <row r="137">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19965,12 +19965,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20097,7 +20097,7 @@
         <v>0</v>
       </c>
       <c r="AO139" s="3" t="n">
-        <v>45891.89583333334</v>
+        <v>45891.875</v>
       </c>
     </row>
     <row r="140">
@@ -20106,12 +20106,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20238,7 +20238,7 @@
         <v>0</v>
       </c>
       <c r="AO140" s="3" t="n">
-        <v>45891.89583333334</v>
+        <v>45891.875</v>
       </c>
     </row>
     <row r="141">
@@ -20247,12 +20247,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20379,7 +20379,7 @@
         <v>0</v>
       </c>
       <c r="AO141" s="3" t="n">
-        <v>45891.89930555555</v>
+        <v>45891.89583333334</v>
       </c>
     </row>
     <row r="142">
@@ -20388,138 +20388,420 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="3" t="n">
+        <v>45891.89583333334</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO143" s="3" t="n">
+        <v>45891.89930555555</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Forge FC</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="inlineStr">
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO142" s="3" t="n">
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO144" s="3" t="n">
         <v>45891.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12146,16 +12146,16 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,10 +12851,10 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="M89" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="N89" t="n">
-        <v>8.5</v>
+        <v>1.36</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="Y89" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15677,10 +15677,10 @@
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO144"/>
+  <dimension ref="A1:AO143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12146,16 +12146,16 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,16 +12428,16 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,10 +12992,10 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15677,10 +15677,10 @@
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
@@ -15740,22 +15740,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20529,12 +20529,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20661,147 +20661,6 @@
         <v>0</v>
       </c>
       <c r="AO143" s="3" t="n">
-        <v>45891.89930555555</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>45891</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Forge FC</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO144" s="3" t="n">
         <v>45891.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>1.85</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,14 +6470,14 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N43" t="n">
         <v>3.75</v>
       </c>
-      <c r="N43" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N44" t="n">
         <v>3.4</v>
-      </c>
-      <c r="M44" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="M60" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.29</v>
+        <v>3.55</v>
       </c>
       <c r="M68" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="M85" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="N85" t="n">
-        <v>8.5</v>
+        <v>1.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,16 +12428,16 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="Y85" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15740,22 +15740,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16100,10 +16100,10 @@
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="M42" t="n">
         <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="M61" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N61" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.49</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.4</v>
+        <v>1.65</v>
       </c>
       <c r="M62" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N62" t="n">
         <v>4.2</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1.58</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="M66" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="M69" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12146,16 +12146,16 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,10 +12428,10 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.28</v>
+        <v>1.35</v>
       </c>
       <c r="M100" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>8.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16100,10 +16100,10 @@
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
         <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.92</v>
+        <v>3.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N44" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="M57" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="M62" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N62" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12146,16 +12146,16 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="M86" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="N86" t="n">
-        <v>1.36</v>
+        <v>8.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12710,10 +12710,10 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.4</v>
+        <v>2.28</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N96" t="n">
-        <v>1.71</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M101" t="n">
         <v>3.2</v>
       </c>
-      <c r="M101" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N101" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="M102" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>3.75</v>
+        <v>1.71</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.12</v>
+        <v>1.8</v>
       </c>
       <c r="M110" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="N110" t="n">
-        <v>1.84</v>
+        <v>4.9</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,16 +15953,16 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16100,10 +16100,10 @@
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N57" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="M69" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N69" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N69" t="n">
-        <v>2.49</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,10 +12428,10 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12710,10 +12710,10 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="M99" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>8.5</v>
+        <v>2.55</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.85</v>
+        <v>1.86</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N101" t="n">
-        <v>2.31</v>
+        <v>3.75</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         <v>1.79</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>4.4</v>
+        <v>1.75</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N103" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N104" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="M105" t="n">
         <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="M110" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N110" t="n">
-        <v>4.9</v>
+        <v>1.87</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,16 +15953,16 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16100,10 +16100,10 @@
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1148,10 +1148,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,14 +6470,14 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N43" t="n">
         <v>3.75</v>
       </c>
-      <c r="N43" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="M55" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N55" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M57" t="n">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N59" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N61" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="M65" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.29</v>
+        <v>3.55</v>
       </c>
       <c r="M69" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.36</v>
+        <v>1.3</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="N88" t="n">
-        <v>2.65</v>
+        <v>8.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="M97" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N97" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N99" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         <v>1.79</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.75</v>
+        <v>4.4</v>
       </c>
       <c r="M103" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>8.5</v>
+        <v>2.31</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="M106" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N108" t="n">
-        <v>4.9</v>
+        <v>1.87</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,16 +15671,16 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
@@ -15740,22 +15740,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="M42" t="n">
         <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,14 +6611,14 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N44" t="n">
         <v>3.4</v>
       </c>
-      <c r="M44" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1.85</v>
-      </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="N57" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="M90" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N90" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,10 +13133,10 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N102" t="n">
-        <v>3.75</v>
+        <v>2.31</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15677,10 +15677,10 @@
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,14 +5624,14 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N37" t="n">
         <v>4.1</v>
       </c>
-      <c r="N37" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.85</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>3.55</v>
       </c>
       <c r="M57" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="M64" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.4</v>
+        <v>2.29</v>
       </c>
       <c r="M65" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N65" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>7.5</v>
+        <v>2.36</v>
       </c>
       <c r="M85" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N85" t="n">
-        <v>1.36</v>
+        <v>2.65</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,10 +12428,10 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,10 +13133,10 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M93" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="M102" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N102" t="n">
-        <v>2.31</v>
+        <v>2.95</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N104" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="M105" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="N105" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M107" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N107" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19301,13 +19301,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19337,10 +19337,10 @@
         <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.76</v>
+        <v>2.94</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>2.01</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N55" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.55</v>
+        <v>2.16</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="M60" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>1.58</v>
+        <v>2.49</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.29</v>
+        <v>4.3</v>
       </c>
       <c r="M65" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N65" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="M67" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,10 +12287,10 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.5</v>
+        <v>1.23</v>
       </c>
       <c r="M86" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="N86" t="n">
-        <v>1.36</v>
+        <v>9.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -13061,22 +13061,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13697,10 +13697,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N100" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="M101" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="N101" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="M102" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N102" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="M104" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N104" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16622,13 +16622,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19865,13 +19865,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19901,10 +19901,10 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.67</v>
+        <v>2.94</v>
       </c>
       <c r="M40" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>2.01</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>3.09</v>
+        <v>3.87</v>
       </c>
       <c r="N62" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="M64" t="n">
         <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="M65" t="n">
-        <v>4.1</v>
+        <v>3.09</v>
       </c>
       <c r="N65" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.63</v>
+        <v>4.3</v>
       </c>
       <c r="M66" t="n">
-        <v>3.87</v>
+        <v>4.1</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>1.56</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="M75" t="n">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="N75" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="M78" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="N78" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.63</v>
+        <v>1.99</v>
       </c>
       <c r="M80" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N80" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12146,10 +12146,10 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>7.3</v>
+        <v>2.29</v>
       </c>
       <c r="M84" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,10 +12287,10 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,16 +12428,16 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13697,10 +13697,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="M95" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>3.75</v>
+        <v>2.31</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M98" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M100" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="M102" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N102" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15959,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16622,13 +16622,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -16799,10 +16799,10 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19301,13 +19301,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19337,10 +19337,10 @@
         <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19865,13 +19865,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19901,10 +19901,10 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G140" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO143"/>
+  <dimension ref="A1:AO144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="M39" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="AO46" s="3" t="n">
-        <v>45891.5625</v>
+        <v>45891.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7557,27 +7557,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45891.58333333334</v>
+        <v>45891.5625</v>
       </c>
     </row>
     <row r="52">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8121,27 +8121,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="AO55" s="3" t="n">
-        <v>45891.60416666666</v>
+        <v>45891.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N60" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="M62" t="n">
-        <v>3.87</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.49</v>
+        <v>2.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N68" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="M69" t="n">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10236,27 +10236,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>45891.62152777778</v>
+        <v>45891.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -10377,27 +10377,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10509,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>45891.625</v>
+        <v>45891.62152777778</v>
       </c>
     </row>
     <row r="72">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="M74" t="n">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="N74" t="n">
-        <v>3.37</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="M75" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11582,10 +11582,10 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -11787,12 +11787,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11919,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>45891.63541666666</v>
+        <v>45891.625</v>
       </c>
     </row>
     <row r="82">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12146,10 +12146,10 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>0</v>
       </c>
       <c r="AO83" s="3" t="n">
-        <v>45891.64583333334</v>
+        <v>45891.63541666666</v>
       </c>
     </row>
     <row r="84">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,16 +12428,16 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -13056,27 +13056,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="AO90" s="3" t="n">
-        <v>45891.65625</v>
+        <v>45891.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N91" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N95" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N97" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M100" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N100" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.35</v>
+        <v>2.28</v>
       </c>
       <c r="M103" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="N103" t="n">
-        <v>8.5</v>
+        <v>2.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
         <v>0</v>
       </c>
       <c r="AO108" s="3" t="n">
-        <v>45891.66666666666</v>
+        <v>45891.65625</v>
       </c>
     </row>
     <row r="109">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16431,7 +16431,7 @@
         <v>0</v>
       </c>
       <c r="AO113" s="3" t="n">
-        <v>45891.67708333334</v>
+        <v>45891.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -16799,10 +16799,10 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17004,12 +17004,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17136,7 +17136,7 @@
         <v>0</v>
       </c>
       <c r="AO118" s="3" t="n">
-        <v>45891.6875</v>
+        <v>45891.67708333334</v>
       </c>
     </row>
     <row r="119">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17427,27 +17427,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17559,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="AO121" s="3" t="n">
-        <v>45891.79166666666</v>
+        <v>45891.6875</v>
       </c>
     </row>
     <row r="122">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19392,7 +19392,7 @@
         <v>0</v>
       </c>
       <c r="AO134" s="3" t="n">
-        <v>45891.83333333334</v>
+        <v>45891.79166666666</v>
       </c>
     </row>
     <row r="135">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19542,12 +19542,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19583,13 +19583,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -19674,7 +19674,7 @@
         <v>0</v>
       </c>
       <c r="AO136" s="3" t="n">
-        <v>45891.85416666666</v>
+        <v>45891.83333333334</v>
       </c>
     </row>
     <row r="137">
@@ -19683,12 +19683,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19815,7 +19815,7 @@
         <v>0</v>
       </c>
       <c r="AO137" s="3" t="n">
-        <v>45891.875</v>
+        <v>45891.85416666666</v>
       </c>
     </row>
     <row r="138">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20147,13 +20147,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -20183,10 +20183,10 @@
         <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
@@ -20247,12 +20247,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20379,7 +20379,7 @@
         <v>0</v>
       </c>
       <c r="AO141" s="3" t="n">
-        <v>45891.89583333334</v>
+        <v>45891.875</v>
       </c>
     </row>
     <row r="142">
@@ -20529,138 +20529,279 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO143" s="3" t="n">
+        <v>45891.89583333334</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Forge FC</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="inlineStr">
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO143" s="3" t="n">
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO144" s="3" t="n">
         <v>45891.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>3.03</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.94</v>
+        <v>1.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.01</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>2.94</v>
       </c>
       <c r="M43" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>2.01</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N61" t="n">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.87</v>
       </c>
       <c r="N62" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N63" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="M68" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N68" t="n">
-        <v>1.56</v>
+        <v>3.25</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="M69" t="n">
-        <v>3.87</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="M74" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="N74" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11582,10 +11582,10 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.3</v>
+        <v>2.29</v>
       </c>
       <c r="M86" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.23</v>
+        <v>7.3</v>
       </c>
       <c r="M88" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="N88" t="n">
-        <v>9.5</v>
+        <v>1.34</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.29</v>
+        <v>1.23</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="N89" t="n">
-        <v>2.57</v>
+        <v>9.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="M91" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M95" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N97" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="M107" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N107" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N108" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15740,22 +15740,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15953,10 +15953,10 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z110" t="n">
         <v>2.37</v>
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,22 +16304,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,10 +16376,10 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19583,13 +19583,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19865,13 +19865,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19901,10 +19901,10 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20147,13 +20147,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -20183,10 +20183,10 @@
         <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.94</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.01</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="M44" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="N44" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.55</v>
+        <v>2.29</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N59" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="N63" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="M68" t="n">
-        <v>3.05</v>
+        <v>3.87</v>
       </c>
       <c r="N68" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N76" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11683,17 +11683,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="M93" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="N93" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>4.4</v>
+        <v>1.86</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N104" t="n">
-        <v>1.71</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.75</v>
+        <v>4.4</v>
       </c>
       <c r="M107" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15812,10 +15812,10 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,16 +15953,16 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16304,22 +16304,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="M113" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N113" t="n">
-        <v>4.9</v>
+        <v>1.87</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,16 +16376,16 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19865,13 +19865,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19901,10 +19901,10 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20288,13 +20288,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -20324,10 +20324,10 @@
         <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>3.38</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>2.17</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.03</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.94</v>
+        <v>1.62</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
-        <v>2.01</v>
+        <v>4.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="M57" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N60" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="M63" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.87</v>
       </c>
       <c r="N65" t="n">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.55</v>
+        <v>2.29</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N66" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.63</v>
+        <v>2.45</v>
       </c>
       <c r="M68" t="n">
-        <v>3.87</v>
+        <v>3.09</v>
       </c>
       <c r="N68" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>2.49</v>
+        <v>2.86</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="M76" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="N76" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11824,17 +11824,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11864,10 +11864,10 @@
         <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z81" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,16 +12428,16 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12710,10 +12710,10 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,10 +12851,10 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="M92" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>8.5</v>
+        <v>2.31</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="M93" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="N93" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.28</v>
+        <v>4.4</v>
       </c>
       <c r="M100" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>1.71</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15740,22 +15740,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="M109" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N109" t="n">
-        <v>4.9</v>
+        <v>1.87</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15812,16 +15812,16 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16304,22 +16304,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,16 +16376,16 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -16799,10 +16799,10 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19583,13 +19583,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19865,13 +19865,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19901,10 +19901,10 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20288,13 +20288,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -20324,10 +20324,10 @@
         <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>1.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="M49" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N49" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="M56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N56" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.49</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.55</v>
+        <v>2.16</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="M60" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N63" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="M66" t="n">
-        <v>2.9</v>
+        <v>3.87</v>
       </c>
       <c r="N66" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="M68" t="n">
-        <v>3.09</v>
+        <v>4.1</v>
       </c>
       <c r="N68" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.63</v>
+        <v>1.97</v>
       </c>
       <c r="M77" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="N77" t="n">
-        <v>2.5</v>
+        <v>3.37</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11582,10 +11582,10 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11824,17 +11824,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11864,10 +11864,10 @@
         <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -12428,16 +12428,16 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12710,10 +12710,10 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,10 +13133,10 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N94" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13697,10 +13697,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N96" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M98" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N98" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="M100" t="n">
         <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M103" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,22 +15035,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="M106" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>3.75</v>
+        <v>1.71</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15812,16 +15812,16 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.69</v>
+        <v>1.8</v>
       </c>
       <c r="M111" t="n">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>2.83</v>
+        <v>4.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="M112" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="N112" t="n">
-        <v>4.9</v>
+        <v>2.83</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16304,22 +16304,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,16 +16376,16 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -16799,10 +16799,10 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19865,13 +19865,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19901,10 +19901,10 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="M45" t="n">
-        <v>3.03</v>
+        <v>3.66</v>
       </c>
       <c r="N45" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="N56" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="M57" t="n">
-        <v>3.05</v>
+        <v>3.87</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="M63" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="M66" t="n">
-        <v>3.87</v>
+        <v>2.9</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="M68" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N79" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11582,10 +11582,10 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12710,10 +12710,10 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>7.3</v>
+        <v>2.29</v>
       </c>
       <c r="M90" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13133,10 +13133,10 @@
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="M94" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>8.5</v>
+        <v>2.31</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13697,10 +13697,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M98" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N100" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M103" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N103" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="M104" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>3.75</v>
+        <v>1.71</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="M105" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N105" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,16 +15953,16 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="N111" t="n">
-        <v>4.9</v>
+        <v>2.83</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.69</v>
+        <v>1.8</v>
       </c>
       <c r="M112" t="n">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>2.83</v>
+        <v>4.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16304,22 +16304,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,16 +16376,16 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19583,13 +19583,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.65</v>
+        <v>1.78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.94</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="N42" t="n">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="M56" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="N56" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N63" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="M66" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M67" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.3</v>
+        <v>1.63</v>
       </c>
       <c r="M70" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N70" t="n">
         <v>4.1</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1.56</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -11123,13 +11123,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -11159,10 +11159,10 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N77" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="N78" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12251,13 +12251,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>7.3</v>
+        <v>2.29</v>
       </c>
       <c r="M87" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12710,10 +12710,10 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.75</v>
+        <v>7.3</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N89" t="n">
-        <v>2.6</v>
+        <v>1.34</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,10 +12992,10 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="M93" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>8.5</v>
+        <v>2.31</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13697,10 +13697,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N96" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="M101" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.07</v>
+        <v>1.75</v>
       </c>
       <c r="M102" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="N102" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.2</v>
+        <v>1.89</v>
       </c>
       <c r="Y102" t="n">
-        <v>4</v>
+        <v>1.79</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="M103" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N103" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>4.4</v>
+        <v>1.35</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N104" t="n">
-        <v>1.71</v>
+        <v>8.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15812,16 +15812,16 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,16 +15953,16 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -16094,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="M112" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="N112" t="n">
-        <v>4.9</v>
+        <v>2.83</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,10 +16376,10 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16622,13 +16622,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19583,13 +19583,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20147,13 +20147,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -20183,10 +20183,10 @@
         <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.67</v>
+        <v>2.94</v>
       </c>
       <c r="M38" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>2.01</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="M56" t="n">
-        <v>2.9</v>
+        <v>3.87</v>
       </c>
       <c r="N56" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="M65" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N65" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N66" t="n">
-        <v>2.86</v>
+        <v>1.56</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>3.09</v>
       </c>
       <c r="N67" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11546,13 +11546,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -11582,10 +11582,10 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.23</v>
+        <v>2.75</v>
       </c>
       <c r="M88" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
-        <v>9.5</v>
+        <v>2.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>7.3</v>
+        <v>1.23</v>
       </c>
       <c r="M89" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="N89" t="n">
-        <v>1.34</v>
+        <v>9.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N93" t="n">
-        <v>2.31</v>
+        <v>8.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13697,10 +13697,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M96" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N96" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14084,13 +14084,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.07</v>
+        <v>2.85</v>
       </c>
       <c r="M99" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="N99" t="n">
-        <v>28</v>
+        <v>2.31</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="M101" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.35</v>
+        <v>1.86</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="N104" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15107,10 +15107,10 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15212,13 +15212,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15248,10 +15248,10 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="M107" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N107" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15530,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z107" t="n">
         <v>0</v>
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,22 +15740,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="M109" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N109" t="n">
-        <v>1.87</v>
+        <v>4.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15812,16 +15812,16 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,10 +15953,10 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z110" t="n">
         <v>0</v>
@@ -16022,22 +16022,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
       <c r="M112" t="n">
-        <v>2.89</v>
+        <v>3.7</v>
       </c>
       <c r="N112" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,16 +16235,16 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y112" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y112" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB112" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,10 +16376,10 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16622,13 +16622,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -16799,10 +16799,10 @@
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19583,13 +19583,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19619,10 +19619,10 @@
         <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20147,13 +20147,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -20183,10 +20183,10 @@
         <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G141" t="n">

--- a/jogos_2025-08-22.xlsx
+++ b/jogos_2025-08-22.xlsx
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1148,10 +1148,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="N6" t="n">
-        <v>1.81</v>
+        <v>3.84</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wikki Tourist</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Wikki Tourist</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.38</v>
+        <v>1.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.81</v>
       </c>
       <c r="N29" t="n">
-        <v>2.17</v>
+        <v>3.52</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>2.94</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>2.01</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.03</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N50" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="M56" t="n">
-        <v>3.87</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9332,10 +9332,10 @@
         <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.29</v>
+        <v>4.3</v>
       </c>
       <c r="M65" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N65" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9614,10 +9614,10 @@
         <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="M67" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="N67" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10319,10 +10319,10 @@
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB70" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.86</v>
       